--- a/BE/FestivalHoa/Properties/TemplateFiles/Lichsucall.xlsx
+++ b/BE/FestivalHoa/Properties/TemplateFiles/Lichsucall.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7510"/>
+    <workbookView windowWidth="19190" windowHeight="7520"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,10 +24,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
-<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData"/>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -64,7 +60,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -80,12 +76,6 @@
     </font>
     <font>
       <b/>
-      <sz val="20"/>
-      <color theme="4" tint="-0.5"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="20"/>
       <color theme="4" tint="-0.5"/>
       <name val="Times New Roman"/>
@@ -590,133 +580,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -727,16 +717,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1275,8 +1265,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="5"/>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="8.72727272727273" style="1"/>
     <col min="3" max="3" width="17.5454545454545" style="1" customWidth="1"/>
@@ -1286,11 +1276,16 @@
     <col min="7" max="16384" width="8.72727272727273" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" spans="4:5">
-      <c r="D1" s="2" t="s">
+    <row r="1" ht="25" spans="1:7">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="3"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
     </row>
     <row r="3" ht="16.5" spans="1:6">
       <c r="A3" s="4" t="s">
@@ -1385,9 +1380,6 @@
       <c r="F12" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="D1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="600"/>
   <headerFooter>
